--- a/InputData/bldgs/BPSfDSPC/BAU Perc Subsidy for Distributed Solar PV Capacity.xlsx
+++ b/InputData/bldgs/BPSfDSPC/BAU Perc Subsidy for Distributed Solar PV Capacity.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\United States\us-eps\InputData\bldgs\BPSfDSPC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RobbieOrvis\Models\EPS Structure Research\eps-us-dc-replay\InputData\bldgs\BPSfDSPC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B439AB3-0459-4198-9F1D-163C78F4AEEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB436DF9-860D-45BE-A552-E764C91C55A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7860" yWindow="1950" windowWidth="20295" windowHeight="12150" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="23520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="7" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>Sources:</t>
   </si>
@@ -68,6 +68,15 @@
       </rPr>
       <t>We include the 30% 25D credit included in the Inflation Reduction Act, which is phased out in 2026</t>
     </r>
+  </si>
+  <si>
+    <t>data centers</t>
+  </si>
+  <si>
+    <t>Data centers</t>
+  </si>
+  <si>
+    <t>Data centers are a separate building type. They get no distributed solar subsidy, because the model does not build distributed solar at data centers (their maximum distributed solar capacity is zero).</t>
   </si>
 </sst>
 </file>
@@ -111,7 +120,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -119,6 +128,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -424,7 +436,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="61.5703125" customWidth="1"/>
@@ -450,6 +462,14 @@
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -463,7 +483,7 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AE4"/>
+  <dimension ref="A1:AE5"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.85546875" customWidth="1"/>
@@ -850,6 +870,101 @@
         <v>0</v>
       </c>
     </row>
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <v>0</v>
+      </c>
+      <c r="Y5">
+        <v>0</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0</v>
+      </c>
+      <c r="AC5">
+        <v>0</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
